--- a/artfynd/A 59566-2021 artfynd.xlsx
+++ b/artfynd/A 59566-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59566-2021 artfynd.xlsx
+++ b/artfynd/A 59566-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14405581</v>
+        <v>17286051</v>
       </c>
       <c r="B2" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väst Skävsta, Vargberget, Vstm</t>
+          <t>Vargberget (ca 450m SO om), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574647.0362422586</v>
+        <v>574609</v>
       </c>
       <c r="R2" t="n">
-        <v>6611735.752237387</v>
+        <v>6611734</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1973-04-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1973-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,36 +764,389 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>i murken tallved</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Peter Rolfson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>PR73-95</t>
+          <t>Äldre mossig granskog nedanför blockrik terräng</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>17286052</v>
+      </c>
+      <c r="B3" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vargberget (ca 450m SO om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>574618</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6611725</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-04-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-04-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog nedanför blockrik terräng</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17286054</v>
+      </c>
+      <c r="B4" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vargberget (ca 450m SO om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>574617</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611718</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-04-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-04-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre mossig granskog nedanför blockrik terräng</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14405581</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6274</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105336</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig flatbagge</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Peltis ferruginea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Väst Skävsta, Vargberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>574647</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611736</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lillhärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1973-04-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1973-04-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>i murken tallved</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
           <t>Peter Rolfson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>PR73-95</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
         <is>
           <t>Peter Rolfson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Peter Rolfson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59566-2021 artfynd.xlsx
+++ b/artfynd/A 59566-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17286051</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17286052</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17286054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,8 +1167,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14405581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>